--- a/data/Plantilla_Inventario_AEMATEC.xlsx
+++ b/data/Plantilla_Inventario_AEMATEC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DYNABOOK\Desktop\TEC\Asocia\Inventario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DYNABOOK\Desktop\TEC\Asocia\Página\Base-de-Datos-AEMATEC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C517CE07-8801-415D-928C-61749CBA1265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E82FA750-4BDB-4A28-8068-E6765FFD0C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="809" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="953">
   <si>
     <t>Bienvenido</t>
   </si>
@@ -1722,12 +1722,6 @@
     <t>Fabio González</t>
   </si>
   <si>
-    <t>BIB-013-01</t>
-  </si>
-  <si>
-    <t>BIB-013-02</t>
-  </si>
-  <si>
     <t>Problemas de Álgebra Moderna</t>
   </si>
   <si>
@@ -2016,9 +2010,6 @@
     <t>BIB-042-01</t>
   </si>
   <si>
-    <t>BIB-042-02</t>
-  </si>
-  <si>
     <t>BIB-042-03</t>
   </si>
   <si>
@@ -2298,15 +2289,6 @@
     <t>Arthur D. Kramer</t>
   </si>
   <si>
-    <t>Temas de Fundamentos de Matemática: Topología</t>
-  </si>
-  <si>
-    <t>Gil Chaverri R.</t>
-  </si>
-  <si>
-    <t>Es muy delgado</t>
-  </si>
-  <si>
     <t>Geometría Analítica y Trigonometría</t>
   </si>
   <si>
@@ -2466,9 +2448,6 @@
     <t>BIB-134</t>
   </si>
   <si>
-    <t>BIB-135</t>
-  </si>
-  <si>
     <t>BIB-136</t>
   </si>
   <si>
@@ -2541,12 +2520,6 @@
     <t>BIB-090-02</t>
   </si>
   <si>
-    <t>Matemática aplicada a las ciencias económico - administrativas</t>
-  </si>
-  <si>
-    <t>Hilda Ma. Córdoba Delezma</t>
-  </si>
-  <si>
     <t>Economía</t>
   </si>
   <si>
@@ -2809,6 +2782,111 @@
   </si>
   <si>
     <t>Bachillerato Matemáticas 1997</t>
+  </si>
+  <si>
+    <t>BIB-013</t>
+  </si>
+  <si>
+    <t>VI Congreso Internacional de Biomatemáticas</t>
+  </si>
+  <si>
+    <t>Universidad Estatal A Distancia</t>
+  </si>
+  <si>
+    <t>Biomatemática</t>
+  </si>
+  <si>
+    <t>Matemática Activa Sétimo año</t>
+  </si>
+  <si>
+    <t>Guiselle Bolaños M. y Mayela Ríos B.</t>
+  </si>
+  <si>
+    <t>Fuzzy Systems Handbook</t>
+  </si>
+  <si>
+    <t>Lotfi A. Zadeh</t>
+  </si>
+  <si>
+    <t>2era</t>
+  </si>
+  <si>
+    <t>Programación/Lógica</t>
+  </si>
+  <si>
+    <t>Matemáticas Universitarias</t>
+  </si>
+  <si>
+    <t>Jack R. Britton, R. Ben Kriegh y Leon W. Rutland</t>
+  </si>
+  <si>
+    <t>Matemática</t>
+  </si>
+  <si>
+    <t>Métodos matemáticos aplicados a las ciencias: V y VI Simposios</t>
+  </si>
+  <si>
+    <t>Revista de la Universidad de Costa Rica</t>
+  </si>
+  <si>
+    <t>13 volumen</t>
+  </si>
+  <si>
+    <t>Ciencia/Tecnología</t>
+  </si>
+  <si>
+    <t>Matemáticas 9</t>
+  </si>
+  <si>
+    <t>Teodora Tsijli Angelaki</t>
+  </si>
+  <si>
+    <t>Ejercicios de Matemáticas para Administración</t>
+  </si>
+  <si>
+    <t>Luis Alejandro Acuña</t>
+  </si>
+  <si>
+    <t>Matemática Básica</t>
+  </si>
+  <si>
+    <t>Cálculo Diferencial e Integral</t>
+  </si>
+  <si>
+    <t>Escuela de matemáticas</t>
+  </si>
+  <si>
+    <t>Java para Estudiantes</t>
+  </si>
+  <si>
+    <t>Douglas Bell y Mikeparr</t>
+  </si>
+  <si>
+    <t>Curso de Trigonometría</t>
+  </si>
+  <si>
+    <t>Edgar Alencar Filho</t>
+  </si>
+  <si>
+    <t>Matemática General</t>
+  </si>
+  <si>
+    <t>BIB-135-01</t>
+  </si>
+  <si>
+    <t>BIB-135-02</t>
+  </si>
+  <si>
+    <t>Matemáticas</t>
+  </si>
+  <si>
+    <t>Javier Etayo, José Colera y Andrés Ruiz</t>
+  </si>
+  <si>
+    <t>1 volumen</t>
+  </si>
+  <si>
+    <t>Matemática Universitaria</t>
   </si>
 </sst>
 </file>
@@ -3118,6 +3196,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7614,7 +7696,7 @@
     </row>
     <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>536</v>
@@ -7646,7 +7728,7 @@
     </row>
     <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>536</v>
@@ -8027,7 +8109,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>564</v>
+        <v>918</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>562</v>
@@ -8057,27 +8139,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>565</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>563</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E21" s="6">
-        <v>1999</v>
+        <v>1975</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>535</v>
       </c>
       <c r="G21" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>56</v>
@@ -8091,7 +8173,7 @@
     </row>
     <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>566</v>
@@ -8100,10 +8182,10 @@
         <v>567</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="E22" s="6">
-        <v>1975</v>
+        <v>1950</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>535</v>
@@ -8123,7 +8205,7 @@
     </row>
     <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>568</v>
@@ -8132,10 +8214,10 @@
         <v>569</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E23" s="6">
-        <v>1950</v>
+        <v>1976</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>535</v>
@@ -8155,7 +8237,7 @@
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>570</v>
@@ -8164,10 +8246,10 @@
         <v>571</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="E24" s="6">
-        <v>1976</v>
+        <v>1990</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>535</v>
@@ -8185,9 +8267,9 @@
         <v>519</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>572</v>
@@ -8196,13 +8278,13 @@
         <v>573</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="E25" s="6">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="G25" s="6">
         <v>1</v>
@@ -8219,22 +8301,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="E26" s="6">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G26" s="6">
         <v>1</v>
@@ -8249,24 +8331,24 @@
         <v>519</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="E27" s="6">
-        <v>1998</v>
+        <v>1980</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G27" s="6">
         <v>1</v>
@@ -8283,22 +8365,22 @@
     </row>
     <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="E28" s="6">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="G28" s="6">
         <v>1</v>
@@ -8315,7 +8397,7 @@
     </row>
     <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>587</v>
@@ -8327,10 +8409,10 @@
         <v>545</v>
       </c>
       <c r="E29" s="6">
-        <v>1985</v>
+        <v>1979</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="G29" s="6">
         <v>1</v>
@@ -8347,22 +8429,22 @@
     </row>
     <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E30" s="6">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G30" s="6">
         <v>1</v>
@@ -8377,30 +8459,30 @@
         <v>519</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>545</v>
+        <v>595</v>
       </c>
       <c r="E31" s="6">
-        <v>1975</v>
+        <v>2003</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G31" s="6">
         <v>1</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>63</v>
@@ -8409,24 +8491,24 @@
         <v>519</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="E32" s="6">
         <v>2003</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G32" s="6">
         <v>1</v>
@@ -8441,9 +8523,9 @@
         <v>519</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>599</v>
@@ -8452,19 +8534,19 @@
         <v>600</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="E33" s="6">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G33" s="6">
         <v>1</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>63</v>
@@ -8473,9 +8555,9 @@
         <v>519</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>601</v>
@@ -8484,13 +8566,13 @@
         <v>602</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E34" s="6">
-        <v>1997</v>
+        <v>530</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>530</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G34" s="6">
         <v>1</v>
@@ -8507,7 +8589,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>603</v>
@@ -8516,13 +8598,13 @@
         <v>604</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>530</v>
+        <v>545</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1993</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G35" s="6">
         <v>1</v>
@@ -8537,9 +8619,9 @@
         <v>519</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>605</v>
@@ -8551,10 +8633,10 @@
         <v>545</v>
       </c>
       <c r="E36" s="6">
-        <v>1993</v>
+        <v>1998</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G36" s="6">
         <v>1</v>
@@ -8571,7 +8653,7 @@
     </row>
     <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>607</v>
@@ -8580,13 +8662,13 @@
         <v>608</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1998</v>
+        <v>530</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>530</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G37" s="6">
         <v>1</v>
@@ -8601,24 +8683,24 @@
         <v>519</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>207</v>
+        <v>610</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>610</v>
-      </c>
       <c r="D38" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>530</v>
+        <v>538</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1998</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G38" s="6">
         <v>1</v>
@@ -8635,13 +8717,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>538</v>
@@ -8650,10 +8732,10 @@
         <v>1998</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G39" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>56</v>
@@ -8665,27 +8747,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>611</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>538</v>
+        <v>595</v>
       </c>
       <c r="E40" s="6">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G40" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>56</v>
@@ -8697,62 +8779,62 @@
         <v>519</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>614</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="E41" s="6">
+        <v>2001</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="E41" s="6">
-        <v>1995</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="G41" s="6">
-        <v>1</v>
-      </c>
-      <c r="H41" s="6" t="s">
+      <c r="C42" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G42" s="6">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>616</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="E42" s="6">
-        <v>2001</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="G42" s="6">
-        <v>1</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>63</v>
@@ -8763,7 +8845,7 @@
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>617</v>
@@ -8772,13 +8854,13 @@
         <v>618</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>530</v>
+        <v>619</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1987</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="G43" s="6">
         <v>1</v>
@@ -8795,22 +8877,22 @@
     </row>
     <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>211</v>
+        <v>623</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="E44" s="6">
         <v>1987</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G44" s="6">
         <v>1</v>
@@ -8827,25 +8909,25 @@
     </row>
     <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E45" s="6">
         <v>1987</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G45" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>56</v>
@@ -8859,28 +8941,28 @@
     </row>
     <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>626</v>
+        <v>212</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>624</v>
+        <v>544</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="E46" s="6">
         <v>1987</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G46" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>63</v>
@@ -8891,22 +8973,22 @@
     </row>
     <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>212</v>
+        <v>642</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>544</v>
-      </c>
       <c r="D47" s="6" t="s">
-        <v>597</v>
+        <v>545</v>
       </c>
       <c r="E47" s="6">
-        <v>1987</v>
+        <v>2011</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="G47" s="6">
         <v>1</v>
@@ -8923,13 +9005,13 @@
     </row>
     <row r="48" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>545</v>
@@ -8938,10 +9020,10 @@
         <v>2011</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G48" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>55</v>
@@ -8953,15 +9035,15 @@
         <v>519</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>545</v>
@@ -8970,13 +9052,13 @@
         <v>2011</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G49" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>63</v>
@@ -8985,56 +9067,56 @@
         <v>519</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>646</v>
+        <v>213</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="D50" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E50" s="6">
+        <v>1977</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="G50" s="6">
+        <v>1</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E50" s="6">
-        <v>2011</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="G50" s="6">
-        <v>3</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="E51" s="6">
+        <v>1967</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>653</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E51" s="6">
-        <v>1977</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>598</v>
       </c>
       <c r="G51" s="6">
         <v>1</v>
@@ -9049,30 +9131,30 @@
         <v>519</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>545</v>
+        <v>645</v>
       </c>
       <c r="E52" s="6">
-        <v>1967</v>
+        <v>1986</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G52" s="6">
         <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>63</v>
@@ -9081,9 +9163,9 @@
         <v>519</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>656</v>
@@ -9092,19 +9174,19 @@
         <v>657</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>647</v>
+        <v>545</v>
       </c>
       <c r="E53" s="6">
-        <v>1986</v>
+        <v>2009</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G53" s="6">
         <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>63</v>
@@ -9113,47 +9195,15 @@
         <v>519</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>659</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E54" s="6">
-        <v>2009</v>
-      </c>
-      <c r="F54" s="6" t="s">
+    <row r="55" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="G54" s="6">
-        <v>1</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>662</v>
-      </c>
       <c r="B55" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>545</v>
@@ -9162,10 +9212,10 @@
         <v>2009</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G55" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>56</v>
@@ -9177,30 +9227,30 @@
         <v>519</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E56" s="6">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>660</v>
+        <v>596</v>
       </c>
       <c r="G56" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>63</v>
@@ -9209,15 +9259,15 @@
         <v>519</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>545</v>
@@ -9226,10 +9276,10 @@
         <v>2010</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G57" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>55</v>
@@ -9241,30 +9291,30 @@
         <v>519</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>672</v>
+        <v>627</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>670</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="E58" s="6">
-        <v>2010</v>
+        <v>1977</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G58" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>63</v>
@@ -9273,24 +9323,24 @@
         <v>519</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1977</v>
+        <v>530</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>530</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G59" s="6">
         <v>1</v>
@@ -9305,41 +9355,41 @@
         <v>519</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E60" s="6">
+        <v>2004</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="G60" s="6">
+        <v>1</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
         <v>630</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>674</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="G60" s="6">
-        <v>1</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>631</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>676</v>
@@ -9348,45 +9398,45 @@
         <v>677</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="E61" s="6">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F61" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="G61" s="6">
+        <v>1</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="G61" s="6">
-        <v>1</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="C62" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="D62" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E62" s="6">
+        <v>1968</v>
+      </c>
+      <c r="F62" s="6" t="s">
         <v>680</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E62" s="6">
-        <v>2008</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>678</v>
       </c>
       <c r="G62" s="6">
         <v>1</v>
@@ -9401,9 +9451,9 @@
         <v>519</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>681</v>
@@ -9412,45 +9462,45 @@
         <v>682</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="E63" s="6">
-        <v>1968</v>
+        <v>2008</v>
       </c>
       <c r="F63" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="G63" s="6">
+        <v>1</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="G63" s="6">
-        <v>1</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1996</v>
+      </c>
+      <c r="F64" s="6" t="s">
         <v>684</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="E64" s="6">
-        <v>2008</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>683</v>
       </c>
       <c r="G64" s="6">
         <v>1</v>
@@ -9464,22 +9514,25 @@
       <c r="J64" s="6" t="s">
         <v>519</v>
       </c>
+      <c r="K64" s="6" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="65" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>688</v>
-      </c>
       <c r="E65" s="6">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>687</v>
@@ -9497,33 +9550,33 @@
         <v>519</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>636</v>
+        <v>690</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>689</v>
       </c>
       <c r="E66" s="6">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G66" s="6">
         <v>1</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>63</v>
@@ -9532,30 +9585,30 @@
         <v>519</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E67" s="6">
         <v>1992</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G67" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>56</v>
@@ -9567,30 +9620,30 @@
         <v>519</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>694</v>
+        <v>635</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E68" s="6">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G68" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>56</v>
@@ -9602,27 +9655,27 @@
         <v>519</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E69" s="6">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G69" s="6">
         <v>1</v>
@@ -9637,27 +9690,27 @@
         <v>519</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E70" s="6">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G70" s="6">
         <v>1</v>
@@ -9672,27 +9725,27 @@
         <v>519</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E71" s="6">
         <v>1990</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G71" s="6">
         <v>1</v>
@@ -9707,27 +9760,27 @@
         <v>519</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E72" s="6">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G72" s="6">
         <v>1</v>
@@ -9742,27 +9795,27 @@
         <v>519</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C73" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>699</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>701</v>
       </c>
       <c r="E73" s="6">
         <v>1991</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G73" s="6">
         <v>1</v>
@@ -9777,27 +9830,27 @@
         <v>519</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E74" s="6">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G74" s="6">
         <v>1</v>
@@ -9812,27 +9865,27 @@
         <v>519</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E75" s="6">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G75" s="6">
         <v>1</v>
@@ -9847,27 +9900,27 @@
         <v>519</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E76" s="6">
         <v>1989</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G76" s="6">
         <v>1</v>
@@ -9882,27 +9935,27 @@
         <v>519</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="E77" s="6">
-        <v>1989</v>
+        <v>545</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>530</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G77" s="6">
         <v>1</v>
@@ -9916,28 +9969,25 @@
       <c r="J77" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="K77" s="6" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B78" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D78" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>707</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>530</v>
+      <c r="E78" s="6">
+        <v>1996</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G78" s="6">
         <v>1</v>
@@ -9951,25 +10001,28 @@
       <c r="J78" s="6" t="s">
         <v>519</v>
       </c>
+      <c r="K78" s="6" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="79" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E79" s="6">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G79" s="6">
         <v>1</v>
@@ -9984,27 +10037,27 @@
         <v>519</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B80" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D80" s="6" t="s">
         <v>708</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>710</v>
       </c>
       <c r="E80" s="6">
         <v>1997</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G80" s="6">
         <v>1</v>
@@ -10019,27 +10072,27 @@
         <v>519</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E81" s="6">
         <v>1997</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G81" s="6">
         <v>1</v>
@@ -10054,27 +10107,27 @@
         <v>519</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="E82" s="6">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G82" s="6">
         <v>1</v>
@@ -10089,27 +10142,27 @@
         <v>519</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E83" s="6">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G83" s="6">
         <v>1</v>
@@ -10124,27 +10177,27 @@
         <v>519</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E84" s="6">
         <v>1998</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G84" s="6">
         <v>1</v>
@@ -10159,27 +10212,27 @@
         <v>519</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E85" s="6">
         <v>1998</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G85" s="6">
         <v>1</v>
@@ -10194,27 +10247,27 @@
         <v>519</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>708</v>
+        <v>731</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>699</v>
+        <v>732</v>
       </c>
       <c r="D86" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E86" s="6">
+        <v>1974</v>
+      </c>
+      <c r="F86" s="6" t="s">
         <v>733</v>
-      </c>
-      <c r="E86" s="6">
-        <v>1998</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>690</v>
       </c>
       <c r="G86" s="6">
         <v>1</v>
@@ -10228,28 +10281,25 @@
       <c r="J86" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="K86" s="6" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>734</v>
       </c>
       <c r="C87" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E87" s="6">
+        <v>1969</v>
+      </c>
+      <c r="F87" s="6" t="s">
         <v>735</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E87" s="6">
-        <v>1974</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>736</v>
       </c>
       <c r="G87" s="6">
         <v>1</v>
@@ -10266,28 +10316,28 @@
     </row>
     <row r="88" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="B88" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="D88" s="6" t="s">
         <v>737</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="D88" s="6" t="s">
+      <c r="E88" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="E88" s="6">
-        <v>1969</v>
-      </c>
       <c r="F88" s="6" t="s">
-        <v>738</v>
+        <v>810</v>
       </c>
       <c r="G88" s="6">
         <v>1</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>63</v>
@@ -10298,25 +10348,25 @@
     </row>
     <row r="89" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>530</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G89" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>57</v>
@@ -10330,25 +10380,25 @@
     </row>
     <row r="90" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>530</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G90" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>57</v>
@@ -10362,25 +10412,25 @@
     </row>
     <row r="91" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="B91" s="6" t="s">
-        <v>747</v>
-      </c>
       <c r="C91" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>530</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G91" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>57</v>
@@ -10394,25 +10444,25 @@
     </row>
     <row r="92" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>530</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G92" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>57</v>
@@ -10426,28 +10476,28 @@
     </row>
     <row r="93" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="B93" s="6" t="s">
-        <v>747</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>739</v>
-      </c>
       <c r="D93" s="6" t="s">
-        <v>740</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>530</v>
+        <v>584</v>
+      </c>
+      <c r="E93" s="6">
+        <v>2005</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G93" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I93" s="6" t="s">
         <v>63</v>
@@ -10458,22 +10508,22 @@
     </row>
     <row r="94" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>586</v>
+        <v>538</v>
       </c>
       <c r="E94" s="6">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G94" s="6">
         <v>1</v>
@@ -10490,28 +10540,28 @@
     </row>
     <row r="95" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>751</v>
+        <v>716</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>749</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="E95" s="6">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G95" s="6">
         <v>1</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I95" s="6" t="s">
         <v>63</v>
@@ -10520,12 +10570,12 @@
         <v>519</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>752</v>
@@ -10534,10 +10584,10 @@
         <v>545</v>
       </c>
       <c r="E96" s="6">
-        <v>1994</v>
+        <v>1983</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="G96" s="6">
         <v>1</v>
@@ -10552,24 +10602,24 @@
         <v>519</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>754</v>
+        <v>922</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>755</v>
+        <v>923</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E97" s="6">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>817</v>
+        <v>902</v>
       </c>
       <c r="G97" s="6">
         <v>1</v>
@@ -10584,65 +10634,62 @@
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B98" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E98" s="6">
+        <v>2001</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="G98" s="6">
+        <v>1</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="B99" s="6" t="s">
         <v>756</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C99" s="6" t="s">
         <v>757</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E98" s="6">
-        <v>1974</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="G98" s="6">
-        <v>1</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
-        <v>722</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>760</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E99" s="6">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="G99" s="6">
         <v>1</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I99" s="6" t="s">
         <v>63</v>
@@ -10651,15 +10698,15 @@
         <v>519</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>545</v>
@@ -10668,36 +10715,39 @@
         <v>1997</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="G100" s="6">
         <v>1</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>63</v>
       </c>
       <c r="J100" s="6" t="s">
         <v>519</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E101" s="6">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>764</v>
@@ -10714,316 +10764,313 @@
       <c r="J101" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="K101" s="6" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>768</v>
+        <v>808</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E102" s="6">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="G102" s="6">
         <v>1</v>
       </c>
       <c r="H102" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A103" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="G103" s="11">
+        <v>1</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I103" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="K103" s="11" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A104" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="G104" s="6">
+        <v>1</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="G105" s="11">
+        <v>1</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="K105" s="11" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E106" s="6">
+        <v>2016</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="G106" s="6">
+        <v>1</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I102" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>815</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>816</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E103" s="6">
-        <v>2009</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="G103" s="6">
-        <v>1</v>
-      </c>
-      <c r="H103" s="6" t="s">
+      <c r="I106" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>819</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E107" s="11">
+        <v>1978</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="G107" s="11">
+        <v>1</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I107" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" s="12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A108" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="E108" s="12">
+        <v>1978</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="G108" s="12">
+        <v>2</v>
+      </c>
+      <c r="H108" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E109" s="11">
+        <v>1991</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>824</v>
+      </c>
+      <c r="G109" s="11">
+        <v>1</v>
+      </c>
+      <c r="H109" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="I103" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
-        <v>727</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>818</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="D104" s="11" t="s">
+      <c r="I109" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J109" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A110" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="D110" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E110" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="F104" s="11" t="s">
-        <v>819</v>
-      </c>
-      <c r="G104" s="11">
-        <v>1</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I104" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="K104" s="11" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A105" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>821</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>707</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="G105" s="6">
-        <v>1</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
-        <v>729</v>
-      </c>
-      <c r="B106" s="11" t="s">
-        <v>822</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="D106" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E106" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="F106" s="11" t="s">
-        <v>819</v>
-      </c>
-      <c r="G106" s="11">
-        <v>1</v>
-      </c>
-      <c r="H106" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I106" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J106" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="K106" s="11" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A107" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>823</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>824</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="E107" s="6">
-        <v>2016</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="G107" s="6">
-        <v>1</v>
-      </c>
-      <c r="H107" s="6" t="s">
+      <c r="F110" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="G110" s="6">
+        <v>1</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I107" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="B108" s="11" t="s">
+      <c r="I110" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J110" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A111" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="B111" s="6" t="s">
         <v>825</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C111" s="6" t="s">
         <v>826</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E108" s="11">
-        <v>1978</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="G108" s="11">
-        <v>1</v>
-      </c>
-      <c r="H108" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I108" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J108" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" s="12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A109" s="12" t="s">
-        <v>828</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>825</v>
-      </c>
-      <c r="C109" s="12" t="s">
-        <v>826</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="E109" s="12">
-        <v>1978</v>
-      </c>
-      <c r="F109" s="12" t="s">
-        <v>817</v>
-      </c>
-      <c r="G109" s="12">
-        <v>2</v>
-      </c>
-      <c r="H109" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I109" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J109" s="12" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="s">
-        <v>772</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>829</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>830</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E110" s="11">
-        <v>1991</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>831</v>
-      </c>
-      <c r="G110" s="11">
-        <v>1</v>
-      </c>
-      <c r="H110" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I110" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J110" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>832</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>833</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>530</v>
@@ -11032,10 +11079,10 @@
         <v>530</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="G111" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>55</v>
@@ -11047,27 +11094,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="112" spans="1:11" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>836</v>
+        <v>767</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>832</v>
+        <v>919</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>833</v>
+        <v>920</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>530</v>
+        <v>545</v>
+      </c>
+      <c r="E112" s="6">
+        <v>1993</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>834</v>
+        <v>921</v>
       </c>
       <c r="G112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>55</v>
@@ -11079,271 +11126,271 @@
         <v>519</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>831</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="G113" s="11">
+        <v>1</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I113" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A114" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="G114" s="6">
+        <v>1</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J114" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A115" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E115" s="11">
+        <v>1988</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="G115" s="11">
+        <v>1</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I115" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A116" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E116" s="6">
+        <v>2013</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="G116" s="6">
+        <v>1</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A117" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E117" s="11">
+        <v>1965</v>
+      </c>
+      <c r="F117" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="G117" s="11">
+        <v>1</v>
+      </c>
+      <c r="H117" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I117" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J117" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="B113" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>838</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E113" s="6">
-        <v>1981</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="G113" s="6">
-        <v>1</v>
-      </c>
-      <c r="H113" s="6" t="s">
+      <c r="B118" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="E118" s="6">
+        <v>1992</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="G118" s="6">
+        <v>1</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" s="11" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A119" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="E119" s="11">
+        <v>2013</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="G119" s="11">
+        <v>1</v>
+      </c>
+      <c r="H119" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I113" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
-        <v>774</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>841</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="E114" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="F114" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="G114" s="11">
-        <v>1</v>
-      </c>
-      <c r="H114" s="11" t="s">
+      <c r="I119" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A120" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E120" s="6">
+        <v>2009</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="G120" s="6">
+        <v>1</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I114" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>842</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>843</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="G115" s="6">
-        <v>1</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="B116" s="11" t="s">
-        <v>844</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>845</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E116" s="11">
-        <v>1988</v>
-      </c>
-      <c r="F116" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="G116" s="11">
-        <v>1</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I116" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J116" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>846</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E117" s="6">
-        <v>2013</v>
-      </c>
-      <c r="F117" s="6" t="s">
+      <c r="I120" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A121" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="B121" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="G117" s="6">
-        <v>1</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
-        <v>778</v>
-      </c>
-      <c r="B118" s="11" t="s">
+      <c r="C121" s="6" t="s">
         <v>849</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E118" s="11">
-        <v>1965</v>
-      </c>
-      <c r="F118" s="11" t="s">
-        <v>851</v>
-      </c>
-      <c r="G118" s="11">
-        <v>1</v>
-      </c>
-      <c r="H118" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I118" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J118" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="E119" s="6">
-        <v>1992</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="G119" s="6">
-        <v>1</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J119" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" s="11" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A120" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="B120" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="E120" s="11">
-        <v>2013</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>854</v>
-      </c>
-      <c r="G120" s="11">
-        <v>1</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I120" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J120" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A121" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>858</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>545</v>
@@ -11352,10 +11399,10 @@
         <v>2009</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="G121" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>55</v>
@@ -11367,379 +11414,379 @@
         <v>519</v>
       </c>
     </row>
-    <row r="122" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>860</v>
+        <v>775</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>545</v>
       </c>
       <c r="E122" s="6">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="F122" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="G122" s="6">
+        <v>1</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I122" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J122" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A123" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="B123" s="11" t="s">
         <v>854</v>
       </c>
-      <c r="G122" s="6">
-        <v>2</v>
-      </c>
-      <c r="H122" s="6" t="s">
+      <c r="C123" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="E123" s="11">
+        <v>2004</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="G123" s="11">
+        <v>1</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I123" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J123" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E124" s="6">
+        <v>1973</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="G124" s="6">
+        <v>1</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I122" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A123" s="6" t="s">
+      <c r="I124" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" s="11" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A125" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>859</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>860</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="E125" s="11">
+        <v>1977</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="G125" s="11">
+        <v>1</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I125" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J125" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E126" s="6">
+        <v>2015</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="G126" s="6">
+        <v>1</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I126" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J126" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A127" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E127" s="11">
+        <v>1994</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>866</v>
+      </c>
+      <c r="G127" s="11">
+        <v>1</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I127" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="B123" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="D123" s="6" t="s">
+      <c r="B128" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="D128" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E123" s="6">
-        <v>2001</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="G123" s="6">
-        <v>1</v>
-      </c>
-      <c r="H123" s="6" t="s">
+      <c r="E128" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="G128" s="6">
+        <v>1</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A129" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E129" s="11">
+        <v>1998</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="G129" s="11">
+        <v>1</v>
+      </c>
+      <c r="H129" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="I123" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J123" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A124" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>863</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>864</v>
-      </c>
-      <c r="D124" s="11" t="s">
+      <c r="I129" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A130" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E130" s="6">
+        <v>2008</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="G130" s="6">
+        <v>1</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J130" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" s="11" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A131" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D131" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="E124" s="11">
-        <v>2004</v>
-      </c>
-      <c r="F124" s="11" t="s">
-        <v>865</v>
-      </c>
-      <c r="G124" s="11">
-        <v>1</v>
-      </c>
-      <c r="H124" s="11" t="s">
+      <c r="E131" s="11">
+        <v>2011</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="G131" s="11">
+        <v>1</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I131" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A132" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E132" s="6">
+        <v>1992</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="G132" s="6">
+        <v>1</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I124" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A125" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E125" s="6">
-        <v>1973</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="G125" s="6">
-        <v>1</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I125" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J125" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" s="11" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
-        <v>784</v>
-      </c>
-      <c r="B126" s="11" t="s">
-        <v>868</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>869</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="E126" s="11">
-        <v>1977</v>
-      </c>
-      <c r="F126" s="11" t="s">
-        <v>576</v>
-      </c>
-      <c r="G126" s="11">
-        <v>1</v>
-      </c>
-      <c r="H126" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I126" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J126" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="B127" s="6" t="s">
+      <c r="I132" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J132" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A133" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="B133" s="6" t="s">
         <v>870</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E127" s="6">
-        <v>2015</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="G127" s="6">
-        <v>1</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J127" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A128" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="B128" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>874</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E128" s="11">
-        <v>1994</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="G128" s="11">
-        <v>1</v>
-      </c>
-      <c r="H128" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I128" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J128" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="6" t="s">
-        <v>787</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C129" s="6" t="s">
+      <c r="C133" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="D129" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>878</v>
-      </c>
-      <c r="G129" s="6">
-        <v>1</v>
-      </c>
-      <c r="H129" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J129" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A130" s="6" t="s">
-        <v>788</v>
-      </c>
-      <c r="B130" s="11" t="s">
-        <v>879</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>880</v>
-      </c>
-      <c r="D130" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E130" s="11">
-        <v>1998</v>
-      </c>
-      <c r="F130" s="11" t="s">
-        <v>839</v>
-      </c>
-      <c r="G130" s="11">
-        <v>1</v>
-      </c>
-      <c r="H130" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I130" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J130" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A131" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>881</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>882</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="E131" s="6">
-        <v>2008</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>883</v>
-      </c>
-      <c r="G131" s="6">
-        <v>1</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J131" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" s="11" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A132" s="6" t="s">
-        <v>790</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>884</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>885</v>
-      </c>
-      <c r="D132" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="E132" s="11">
-        <v>2011</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="G132" s="11">
-        <v>1</v>
-      </c>
-      <c r="H132" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I132" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J132" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A133" s="6" t="s">
-        <v>887</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>886</v>
-      </c>
       <c r="D133" s="6" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E133" s="6">
         <v>1992</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="G133" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>56</v>
@@ -11751,207 +11798,207 @@
         <v>519</v>
       </c>
     </row>
-    <row r="134" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="G134" s="6">
+        <v>1</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J134" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A135" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="E135" s="11">
+        <v>2014</v>
+      </c>
+      <c r="F135" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="G135" s="11">
+        <v>1</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I135" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A136" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E136" s="6">
+        <v>1998</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="G136" s="6">
+        <v>1</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J136" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="C137" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="B134" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>886</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="E134" s="6">
-        <v>1992</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="G134" s="6">
-        <v>2</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A135" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="B135" s="6" t="s">
+      <c r="D137" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="E137" s="11">
+        <v>2015</v>
+      </c>
+      <c r="F137" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="G137" s="11">
+        <v>1</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I137" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J137" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A138" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>889</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>816</v>
-      </c>
-      <c r="D135" s="6" t="s">
+      <c r="D138" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="E135" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="G135" s="6">
-        <v>1</v>
-      </c>
-      <c r="H135" s="6" t="s">
+      <c r="E138" s="6">
+        <v>1999</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="G138" s="6">
+        <v>1</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I135" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J135" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="6" t="s">
-        <v>792</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>890</v>
-      </c>
-      <c r="C136" s="11" t="s">
+      <c r="I138" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J138" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" s="11" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A139" s="6" t="s">
         <v>891</v>
       </c>
-      <c r="D136" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="E136" s="11">
-        <v>2014</v>
-      </c>
-      <c r="F136" s="11" t="s">
+      <c r="B139" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="E139" s="11">
+        <v>2012</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="G139" s="11">
+        <v>1</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I139" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J139" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A140" s="6" t="s">
         <v>892</v>
       </c>
-      <c r="G136" s="11">
-        <v>1</v>
-      </c>
-      <c r="H136" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I136" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J136" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A137" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>895</v>
-      </c>
-      <c r="C137" s="6" t="s">
+      <c r="B140" s="11" t="s">
         <v>893</v>
       </c>
-      <c r="D137" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="E137" s="6">
-        <v>1998</v>
-      </c>
-      <c r="F137" s="6" t="s">
+      <c r="C140" s="11" t="s">
         <v>894</v>
-      </c>
-      <c r="G137" s="6">
-        <v>1</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J137" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="6" t="s">
-        <v>794</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>896</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>897</v>
-      </c>
-      <c r="D138" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="E138" s="11">
-        <v>2015</v>
-      </c>
-      <c r="F138" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="G138" s="11">
-        <v>1</v>
-      </c>
-      <c r="H138" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I138" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J138" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A139" s="6" t="s">
-        <v>795</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>916</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>898</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E139" s="6">
-        <v>1999</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>899</v>
-      </c>
-      <c r="G139" s="6">
-        <v>1</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J139" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" s="11" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A140" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>902</v>
-      </c>
-      <c r="C140" s="11" t="s">
-        <v>903</v>
       </c>
       <c r="D140" s="11" t="s">
         <v>545</v>
@@ -11960,13 +12007,13 @@
         <v>2012</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="G140" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>63</v>
@@ -11975,27 +12022,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>545</v>
+        <v>645</v>
       </c>
       <c r="E141" s="11">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="G141" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" s="11" t="s">
         <v>56</v>
@@ -12007,27 +12054,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="142" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E142" s="11">
         <v>2006</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="G142" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="11" t="s">
         <v>56</v>
@@ -12039,27 +12086,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
-        <v>908</v>
+        <v>790</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>647</v>
+        <v>545</v>
       </c>
       <c r="E143" s="11">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G143" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143" s="11" t="s">
         <v>56</v>
@@ -12071,111 +12118,111 @@
         <v>519</v>
       </c>
     </row>
-    <row r="144" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
-        <v>796</v>
-      </c>
-      <c r="B144" s="11" t="s">
+        <v>791</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>902</v>
+      </c>
+      <c r="G144" s="6">
+        <v>1</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J144" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E145" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="F145" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="G145" s="11">
+        <v>1</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I145" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J145" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="C144" s="11" t="s">
-        <v>910</v>
-      </c>
-      <c r="D144" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="E144" s="11">
-        <v>2009</v>
-      </c>
-      <c r="F144" s="11" t="s">
+      <c r="D146" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>902</v>
+      </c>
+      <c r="G146" s="6">
+        <v>1</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J146" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A147" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="G144" s="11">
-        <v>1</v>
-      </c>
-      <c r="H144" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I144" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J144" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A145" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="G145" s="6">
-        <v>1</v>
-      </c>
-      <c r="H145" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J145" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="B146" s="11" t="s">
-        <v>914</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>915</v>
-      </c>
-      <c r="D146" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E146" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="F146" s="11" t="s">
-        <v>911</v>
-      </c>
-      <c r="G146" s="11">
-        <v>1</v>
-      </c>
-      <c r="H146" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I146" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J146" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A147" s="6" t="s">
-        <v>919</v>
-      </c>
       <c r="B147" s="6" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>530</v>
@@ -12184,10 +12231,10 @@
         <v>530</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="G147" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>56</v>
@@ -12199,27 +12246,27 @@
         <v>519</v>
       </c>
     </row>
-    <row r="148" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>920</v>
+        <v>793</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>918</v>
+        <v>897</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>530</v>
+        <v>645</v>
+      </c>
+      <c r="E148" s="6">
+        <v>1991</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="G148" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>56</v>
@@ -12231,219 +12278,462 @@
         <v>519</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>913</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>897</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="E149" s="11">
+        <v>1992</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="G149" s="11">
+        <v>1</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I149" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J149" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E150" s="6">
+        <v>1992</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>902</v>
+      </c>
+      <c r="G150" s="6">
+        <v>1</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J150" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>915</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>916</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="E151" s="11">
+        <v>2016</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="G151" s="11">
+        <v>1</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I151" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J151" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A152" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E152" s="6">
+        <v>1997</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="G152" s="6">
+        <v>1</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J152" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A153" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>925</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="E153" s="11">
+        <v>1998</v>
+      </c>
+      <c r="F153" s="11" t="s">
+        <v>927</v>
+      </c>
+      <c r="G153" s="11">
+        <v>1</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I153" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="B149" s="6" t="s">
-        <v>921</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>906</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="E149" s="6">
-        <v>1991</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="G149" s="6">
-        <v>1</v>
-      </c>
-      <c r="H149" s="6" t="s">
+      <c r="B154" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E154" s="6">
+        <v>1997</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="G154" s="6">
+        <v>1</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J154" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A155" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>931</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>932</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>933</v>
+      </c>
+      <c r="E155" s="11">
+        <v>1989</v>
+      </c>
+      <c r="F155" s="11" t="s">
+        <v>934</v>
+      </c>
+      <c r="G155" s="11">
+        <v>1</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I155" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E156" s="6">
+        <v>1997</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="G156" s="6">
+        <v>1</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J156" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A157" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>937</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>938</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E157" s="11">
+        <v>2008</v>
+      </c>
+      <c r="F157" s="11" t="s">
+        <v>939</v>
+      </c>
+      <c r="G157" s="11">
+        <v>1</v>
+      </c>
+      <c r="H157" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I157" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J157" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="G158" s="6">
+        <v>1</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J158" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>942</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="E159" s="11">
+        <v>2011</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="G159" s="11">
+        <v>1</v>
+      </c>
+      <c r="H159" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I159" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J159" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E160" s="6">
+        <v>1977</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="G160" s="6">
+        <v>1</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I149" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J149" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="B150" s="11" t="s">
-        <v>922</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>906</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="E150" s="11">
-        <v>1992</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>911</v>
-      </c>
-      <c r="G150" s="11">
-        <v>1</v>
-      </c>
-      <c r="H150" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I150" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J150" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>906</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="E151" s="6">
-        <v>1992</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="G151" s="6">
-        <v>1</v>
-      </c>
-      <c r="H151" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I151" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J151" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A152" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>924</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>925</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="E152" s="11">
-        <v>2016</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>904</v>
-      </c>
-      <c r="G152" s="11">
-        <v>1</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I152" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J152" s="11" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>926</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>918</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E153" s="6">
+      <c r="I160" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J160" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A161" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>950</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>951</v>
+      </c>
+      <c r="E161" s="11">
         <v>1997</v>
       </c>
-      <c r="F153" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="G153" s="6">
-        <v>1</v>
-      </c>
-      <c r="H153" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I153" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J153" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A155" s="6" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="6" t="s">
+      <c r="F161" s="11" t="s">
+        <v>952</v>
+      </c>
+      <c r="G161" s="11">
+        <v>2</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I161" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J161" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="C162" s="11" t="s">
+        <v>950</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>951</v>
+      </c>
+      <c r="E162" s="11">
+        <v>1997</v>
+      </c>
+      <c r="F162" s="11" t="s">
+        <v>952</v>
+      </c>
+      <c r="G162" s="11">
+        <v>2</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I162" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J162" s="11" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="6" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A157" s="6" t="s">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A164" s="6" t="s">
         <v>807</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="6" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A159" s="6" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="6" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" s="6" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" s="6" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="6" t="s">
-        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -13419,8 +13709,262 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009B6E0CC4907A074A895F778C3021B9B3" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d2fa86cfbf994c4eff3fdb42898808ab">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7d25543e-feea-43c7-9776-01627396393f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a0b155c40d372ca09955a33eab7ccfc" ns3:_="">
+    <xsd:import namespace="7d25543e-feea-43c7-9776-01627396393f"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7d25543e-feea-43c7-9776-01627396393f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="11" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="12" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="14" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7d25543e-feea-43c7-9776-01627396393f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4148188F-9690-4A9B-8DC2-D5B63D0C5C75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7d25543e-feea-43c7-9776-01627396393f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCB0C020-43CF-4680-BCB8-33959FE70E00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61B9CDB8-5A96-4897-A204-31A7F67F2DBE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7d25543e-feea-43c7-9776-01627396393f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>